--- a/12-upload_file_merge_file/uploads/pub_cd_map-test4.xlsx
+++ b/12-upload_file_merge_file/uploads/pub_cd_map-test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\12-upload_file_merge_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB141349-527B-480A-99C0-04AD2F3A121F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BF8A83-F1AA-4F0F-849F-F059F1650E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t>取数来源应用</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -151,6 +151,124 @@
   </si>
   <si>
     <t>LINE66666</t>
+  </si>
+  <si>
+    <t>LINE66667</t>
+  </si>
+  <si>
+    <t>LINE66668</t>
+  </si>
+  <si>
+    <t>LINE66669</t>
+  </si>
+  <si>
+    <t>LINE66670</t>
+  </si>
+  <si>
+    <t>LINE66671</t>
+  </si>
+  <si>
+    <t>LINE66672</t>
+  </si>
+  <si>
+    <t>LINE66673</t>
+  </si>
+  <si>
+    <t>LINE66674</t>
+  </si>
+  <si>
+    <t>LINE66675</t>
+  </si>
+  <si>
+    <t>LINE66676</t>
+  </si>
+  <si>
+    <t>LINE66677</t>
+  </si>
+  <si>
+    <t>LINE66678</t>
+  </si>
+  <si>
+    <t>LINE66679</t>
+  </si>
+  <si>
+    <t>LINE66680</t>
+  </si>
+  <si>
+    <t>LINE66681</t>
+  </si>
+  <si>
+    <t>LINE66682</t>
+  </si>
+  <si>
+    <t>LINE66683</t>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
 </sst>
 </file>
@@ -223,12 +341,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -509,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.5546875" customWidth="1"/>
@@ -621,8 +740,8 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="F3" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -665,8 +784,8 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -709,8 +828,8 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>1</v>
+      <c r="F5" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -753,8 +872,8 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>1</v>
+      <c r="F6" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -797,8 +916,8 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>1</v>
+      <c r="F7" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -841,8 +960,8 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="F8" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -851,7 +970,7 @@
         <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -866,6 +985,710 @@
         <v>2</v>
       </c>
       <c r="N8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>47</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
         <v>2</v>
       </c>
     </row>

--- a/12-upload_file_merge_file/uploads/pub_cd_map-test4.xlsx
+++ b/12-upload_file_merge_file/uploads/pub_cd_map-test4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\12-upload_file_merge_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BF8A83-F1AA-4F0F-849F-F059F1650E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BC37E5-A2CC-4FA1-9C0C-F6C104E14FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="74">
   <si>
     <t>取数来源应用</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -223,9 +223,6 @@
     <t>06</t>
   </si>
   <si>
-    <t>07</t>
-  </si>
-  <si>
     <t>08</t>
   </si>
   <si>
@@ -269,6 +266,22 @@
   </si>
   <si>
     <t>22</t>
+  </si>
+  <si>
+    <t>09910</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0544442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -341,13 +354,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -633,7 +650,9 @@
   <cols>
     <col min="1" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="16.21875" customWidth="1"/>
-    <col min="4" max="14" width="14.5546875" customWidth="1"/>
+    <col min="4" max="11" width="14.5546875" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" style="3" customWidth="1"/>
+    <col min="13" max="14" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -670,7 +689,7 @@
       <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -714,7 +733,7 @@
       <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M2" s="2" t="s">
@@ -758,7 +777,7 @@
       <c r="K3">
         <v>2</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="3">
         <v>2</v>
       </c>
       <c r="M3">
@@ -802,7 +821,7 @@
       <c r="K4">
         <v>2</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="3">
         <v>2</v>
       </c>
       <c r="M4">
@@ -846,7 +865,7 @@
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="3">
         <v>2</v>
       </c>
       <c r="M5">
@@ -890,7 +909,7 @@
       <c r="K6">
         <v>2</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="3">
         <v>2</v>
       </c>
       <c r="M6">
@@ -934,7 +953,7 @@
       <c r="K7">
         <v>2</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="3">
         <v>2</v>
       </c>
       <c r="M7">
@@ -978,7 +997,7 @@
       <c r="K8">
         <v>2</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="3">
         <v>2</v>
       </c>
       <c r="M8">
@@ -1005,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1022,8 +1041,8 @@
       <c r="K9">
         <v>2</v>
       </c>
-      <c r="L9">
-        <v>2</v>
+      <c r="L9" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="M9">
         <v>2</v>
@@ -1049,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1066,7 +1085,7 @@
       <c r="K10">
         <v>2</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="3">
         <v>2</v>
       </c>
       <c r="M10">
@@ -1093,7 +1112,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1110,7 +1129,7 @@
       <c r="K11">
         <v>2</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="3">
         <v>2</v>
       </c>
       <c r="M11">
@@ -1137,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1154,7 +1173,7 @@
       <c r="K12">
         <v>2</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="3">
         <v>2</v>
       </c>
       <c r="M12">
@@ -1181,7 +1200,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1198,7 +1217,7 @@
       <c r="K13">
         <v>2</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="3">
         <v>2</v>
       </c>
       <c r="M13">
@@ -1225,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1242,8 +1261,8 @@
       <c r="K14">
         <v>2</v>
       </c>
-      <c r="L14">
-        <v>2</v>
+      <c r="L14" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="M14">
         <v>2</v>
@@ -1269,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1286,7 +1305,7 @@
       <c r="K15">
         <v>2</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="3">
         <v>2</v>
       </c>
       <c r="M15">
@@ -1313,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1330,7 +1349,7 @@
       <c r="K16">
         <v>2</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="3">
         <v>2</v>
       </c>
       <c r="M16">
@@ -1357,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1374,7 +1393,7 @@
       <c r="K17">
         <v>2</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="3">
         <v>2</v>
       </c>
       <c r="M17">
@@ -1401,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1418,7 +1437,7 @@
       <c r="K18">
         <v>2</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="3">
         <v>2</v>
       </c>
       <c r="M18">
@@ -1445,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1462,8 +1481,8 @@
       <c r="K19">
         <v>2</v>
       </c>
-      <c r="L19">
-        <v>2</v>
+      <c r="L19" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="M19">
         <v>2</v>
@@ -1489,7 +1508,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1506,7 +1525,7 @@
       <c r="K20">
         <v>2</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="3">
         <v>2</v>
       </c>
       <c r="M20">
@@ -1533,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1550,7 +1569,7 @@
       <c r="K21">
         <v>2</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="3">
         <v>2</v>
       </c>
       <c r="M21">
@@ -1577,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1594,7 +1613,7 @@
       <c r="K22">
         <v>2</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="3">
         <v>2</v>
       </c>
       <c r="M22">
@@ -1621,7 +1640,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1638,7 +1657,7 @@
       <c r="K23">
         <v>2</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="3">
         <v>2</v>
       </c>
       <c r="M23">
@@ -1665,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1682,7 +1701,7 @@
       <c r="K24">
         <v>2</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="3">
         <v>2</v>
       </c>
       <c r="M24">
